--- a/data/google_news_dedup_audit_27_0426_UTC.xlsx
+++ b/data/google_news_dedup_audit_27_0426_UTC.xlsx
@@ -445,253 +445,253 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8097987771034241</v>
+        <v>0.8795361518859863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Amazon introduces 1-hour and 3-hour delivery in US - MSN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Amazon to take ‘Now’ service to 100 cities, ramps up quick commerce bet - Fortune India</t>
+          <t>Amazon launches 1-hour delivery in hundreds of US cities - MSN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7989979982376099</v>
+        <v>0.7036930322647095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Amazon to take 'Now' rapid-delivery service to 100 cities in India - Business Standard</t>
+          <t>Amazon expands Amazon Now quick commerce service to 100 cities across India, strengthens delivery network - Business Review Live</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6813130378723145</v>
+        <v>0.7036917805671692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Amazon Now to expand to 100 cities with over 1,000 micro-fulfillment centers - Storyboard18</t>
+          <t>Amazon Now targets 1,000 micro-fulfilment centres across 100 cities - financialexpress.com</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7040416598320007</v>
+        <v>0.7311445474624634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Amazon Now to reach 100 cities with 1,000 plus centres in Rs 2,800 crore push - Indian Television Dot Com</t>
+          <t>Amazon to take 'Now' quick-commerce service to 100 cities at Rs 2,800 Cr investment - Dailyhunt</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9113508462905884</v>
+        <v>0.730886697769165</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Man levensgevaarlijk gewond na steekpartij in Merksplas - rtv.be</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Amazon expands Amazon Now quick commerce service to 100 cities across India, strengthens delivery network - Business Review Live</t>
+          <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6929404735565186</v>
+        <v>0.7541934251785278</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amazon to expand quick commerce service 'Amazon Now' to 100 cities across India - The New Indian Express</t>
+          <t>Man levensgevaarlijk gewond na steekpartij in Merksplas - rtv.be</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Amazon to take 'Now' quick-commerce service to 100 cities at Rs 2,800 Cr investment - Dailyhunt</t>
+          <t>Man (34) levensgevaarlijk gewond bij steekpartij in woning in Merksplas: verdachte (22) opgepakt - HLN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>0.730886697769165</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Man levensgevaarlijk gewond na steekpartij in Merksplas - rtv.be</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Man levensgevaarlijk gewond na steekpartij in Merksplas - rtv.be</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6832482814788818</v>
+        <v>0.8945808410644531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
+          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Man (34) levensgevaarlijk gewond bij steekpartij in woning in Merksplas: verdachte (22) opgepakt - HLN</t>
+          <t>Afghan migrant charged with murder of man in west London admits stabbing two people - lbc.co.uk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9999998807907104</v>
+        <v>0.9367899298667908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
+          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Man (34) in levensgevaar na steekpartij in centrum van Merksplas: verdachte opgepakt - Nieuwsblad</t>
+          <t>Afghan migrant admits stabbing two people in London - London Now</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8945808410644531</v>
+        <v>0.7552604675292969</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
+          <t>Boy, 17, left with potentially life changing injuries after stabbing in Westminster - London Now</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Afghan migrant charged with murder of man in west London admits stabbing two people - lbc.co.uk</t>
+          <t>Sixth form 'gave first aid to stabbed boy, 17,' after parent found him injured - London Now</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9367899298667908</v>
+        <v>0.7546032667160034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Afghan migrant admits stabbing two people in west London - Sky News</t>
+          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Afghan migrant admits stabbing two people in London - London Now</t>
+          <t>Reform UK’s Whitehall fuel protest stalls as barely anyone turns up - London Evening Standard</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7646713256835938</v>
+        <v>0.7207223176956177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>London fuel tax protest LIVE: Demonstrators set to gather in Whitehall for Reform-organised 'national rally' - AOL.com</t>
+          <t>Una falsa amenaza de bomba obliga a desalojar un tren de Cercanías en Pozuelo de Alarcón - ABC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Fuel protesters set to descend on London in major national demonstration - London Evening Standard</t>
+          <t>Una falsa amenaza de bomba obligar a desalojar un tren de Cercanías en Pozuelo: el presunto autor ya ha sido detenido - El Periódico de España</t>
         </is>
       </c>
     </row>
